--- a/Assets/Config/Holmas_MapTable.xlsx
+++ b/Assets/Config/Holmas_MapTable.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitHub\Holmas\Assets\Config\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DB507F5A-A85F-4403-9AEB-369D3F045E98}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F0F6862-5C29-4295-8511-22071AA8EDA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{1BF42B18-A502-4721-8DA9-52AB8CB1DBB0}"/>
+    <workbookView xWindow="4960" yWindow="3190" windowWidth="19200" windowHeight="11170" xr2:uid="{1BF42B18-A502-4721-8DA9-52AB8CB1DBB0}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="38">
   <si>
     <t>地图id</t>
   </si>
@@ -66,37 +66,92 @@
     <t>map_001</t>
   </si>
   <si>
-    <t>Assets/HotUpdateContent/Res/Map/1.asset</t>
-  </si>
-  <si>
-    <t>15</t>
-  </si>
-  <si>
-    <t>12</t>
-  </si>
-  <si>
     <t>map_002</t>
   </si>
   <si>
-    <t>Assets/HotUpdateContent/Res/Map/2.asset</t>
-  </si>
-  <si>
-    <t>18</t>
-  </si>
-  <si>
-    <t>14</t>
-  </si>
-  <si>
     <t>map_003</t>
   </si>
   <si>
-    <t>Assets/HotUpdateContent/Res/Map/3.asset</t>
-  </si>
-  <si>
-    <t>20</t>
-  </si>
-  <si>
-    <t>16</t>
+    <t>Assets/HotUpdateContent/Res/Map/11-8-8.asset</t>
+  </si>
+  <si>
+    <t>map_004</t>
+  </si>
+  <si>
+    <t>map_005</t>
+  </si>
+  <si>
+    <t>map_006</t>
+  </si>
+  <si>
+    <t>map_007</t>
+  </si>
+  <si>
+    <t>map_008</t>
+  </si>
+  <si>
+    <t>Assets/HotUpdateContent/Res/Map/11-9-9.asset</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>map_009</t>
+  </si>
+  <si>
+    <t>map_010</t>
+  </si>
+  <si>
+    <t>map_011</t>
+  </si>
+  <si>
+    <t>map_012</t>
+  </si>
+  <si>
+    <t>map_013</t>
+  </si>
+  <si>
+    <t>map_014</t>
+  </si>
+  <si>
+    <t>map_015</t>
+  </si>
+  <si>
+    <t>map_016</t>
+  </si>
+  <si>
+    <t>map_017</t>
+  </si>
+  <si>
+    <t>map_018</t>
+  </si>
+  <si>
+    <t>map_019</t>
+  </si>
+  <si>
+    <t>map_020</t>
+  </si>
+  <si>
+    <t>map_021</t>
+  </si>
+  <si>
+    <t>map_022</t>
+  </si>
+  <si>
+    <t>map_023</t>
+  </si>
+  <si>
+    <t>map_024</t>
+  </si>
+  <si>
+    <t>Assets/HotUpdateContent/Res/Map/11-10-10.asset</t>
+  </si>
+  <si>
+    <t>Assets/HotUpdateContent/Res/Map/11-11-11.asset</t>
+  </si>
+  <si>
+    <t>Assets/HotUpdateContent/Res/Map/11-12-12.asset</t>
+  </si>
+  <si>
+    <t>Assets/HotUpdateContent/Res/Map/11-13-13.asset</t>
   </si>
 </sst>
 </file>
@@ -521,8 +576,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{537D5B2F-D815-43F0-9E00-860E54D6EE48}">
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:D26"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="8.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="42.58203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.9140625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
@@ -531,11 +592,11 @@
       <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" s="2" t="s">
         <v>2</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>3</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
@@ -545,11 +606,11 @@
       <c r="B2" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="C2" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" s="5" t="s">
         <v>6</v>
-      </c>
-      <c r="D2" s="6" t="s">
-        <v>7</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
@@ -557,41 +618,335 @@
         <v>8</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D3" s="3" t="s">
         <v>11</v>
+      </c>
+      <c r="C3" s="3">
+        <v>11</v>
+      </c>
+      <c r="D3" s="2">
+        <v>14</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C4" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" s="6">
         <v>14</v>
       </c>
-      <c r="D4" s="6" t="s">
-        <v>15</v>
+      <c r="D4" s="5">
+        <v>16</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" s="3">
         <v>16</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="D5" s="2">
         <v>17</v>
       </c>
-      <c r="C5" s="2" t="s">
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A6" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C6" s="3">
+        <v>17</v>
+      </c>
+      <c r="D6" s="2">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A7" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" s="3">
+        <v>14</v>
+      </c>
+      <c r="D7" s="2">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A8" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C8" s="6">
+        <v>17</v>
+      </c>
+      <c r="D8" s="5">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A9" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C9" s="3">
+        <v>20</v>
+      </c>
+      <c r="D9" s="2">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A10" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C10" s="3">
+        <v>22</v>
+      </c>
+      <c r="D10" s="2">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A11" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="B11" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C11" s="3">
+        <v>18</v>
+      </c>
+      <c r="D11" s="2">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A12" s="1" t="s">
         <v>19</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C12" s="6">
+        <v>22</v>
+      </c>
+      <c r="D12" s="5">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A13" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C13" s="3">
+        <v>25</v>
+      </c>
+      <c r="D13" s="2">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A14" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C14" s="3">
+        <v>28</v>
+      </c>
+      <c r="D14" s="2">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A15" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C15" s="3">
+        <v>21</v>
+      </c>
+      <c r="D15" s="2">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A16" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C16" s="6">
+        <v>26</v>
+      </c>
+      <c r="D16" s="5">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A17" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C17" s="3">
+        <v>30</v>
+      </c>
+      <c r="D17" s="2">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A18" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C18" s="3">
+        <v>33</v>
+      </c>
+      <c r="D18" s="2">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A19" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C19" s="3">
+        <v>25</v>
+      </c>
+      <c r="D19" s="2">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A20" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C20" s="6">
+        <v>31</v>
+      </c>
+      <c r="D20" s="5">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A21" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C21" s="3">
+        <v>36</v>
+      </c>
+      <c r="D21" s="2">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A22" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C22" s="3">
+        <v>40</v>
+      </c>
+      <c r="D22" s="2">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A23" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C23" s="3">
+        <v>30</v>
+      </c>
+      <c r="D23" s="2">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A24" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C24" s="6">
+        <v>37</v>
+      </c>
+      <c r="D24" s="5">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A25" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C25" s="3">
+        <v>42</v>
+      </c>
+      <c r="D25" s="2">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A26" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C26" s="3">
+        <v>47</v>
+      </c>
+      <c r="D26" s="2">
+        <v>50</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Config/Holmas_MapTable.xlsx
+++ b/Assets/Config/Holmas_MapTable.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitHub\Holmas\Assets\Config\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F0F6862-5C29-4295-8511-22071AA8EDA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C3EABEB-C1D9-4806-BC1B-68348223F830}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4960" yWindow="3190" windowWidth="19200" windowHeight="11170" xr2:uid="{1BF42B18-A502-4721-8DA9-52AB8CB1DBB0}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{1BF42B18-A502-4721-8DA9-52AB8CB1DBB0}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>

--- a/Assets/Config/Holmas_MapTable.xlsx
+++ b/Assets/Config/Holmas_MapTable.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitHub\Holmas\Assets\Config\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C3EABEB-C1D9-4806-BC1B-68348223F830}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23E34427-7013-4C03-889E-A1408476D134}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{1BF42B18-A502-4721-8DA9-52AB8CB1DBB0}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="584" uniqueCount="368">
   <si>
     <t>地图id</t>
   </si>
@@ -63,95 +63,1088 @@
     <t>catCountMin</t>
   </si>
   <si>
-    <t>map_001</t>
-  </si>
-  <si>
-    <t>map_002</t>
-  </si>
-  <si>
-    <t>map_003</t>
-  </si>
-  <si>
     <t>Assets/HotUpdateContent/Res/Map/11-8-8.asset</t>
   </si>
   <si>
-    <t>map_004</t>
-  </si>
-  <si>
-    <t>map_005</t>
-  </si>
-  <si>
-    <t>map_006</t>
-  </si>
-  <si>
-    <t>map_007</t>
-  </si>
-  <si>
-    <t>map_008</t>
+    <t>Assets/HotUpdateContent/Res/Map/11-10-10.asset</t>
+  </si>
+  <si>
+    <t>Assets/HotUpdateContent/Res/Map/11-11-11.asset</t>
+  </si>
+  <si>
+    <t>Assets/HotUpdateContent/Res/Map/11-12-12.asset</t>
+  </si>
+  <si>
+    <t>Assets/HotUpdateContent/Res/Map/11-13-13.asset</t>
+  </si>
+  <si>
+    <t>Assets/HotUpdateContent/Res/Map/12-8-8.asset</t>
+  </si>
+  <si>
+    <t>Assets/HotUpdateContent/Res/Map/13-8-8.asset</t>
+  </si>
+  <si>
+    <t>Assets/HotUpdateContent/Res/Map/14-8-8.asset</t>
+  </si>
+  <si>
+    <t>Assets/HotUpdateContent/Res/Map/15-8-8.asset</t>
+  </si>
+  <si>
+    <t>Assets/HotUpdateContent/Res/Map/17-8-8.asset</t>
+  </si>
+  <si>
+    <t>Assets/HotUpdateContent/Res/Map/18-8-8.asset</t>
   </si>
   <si>
     <t>Assets/HotUpdateContent/Res/Map/11-9-9.asset</t>
+  </si>
+  <si>
+    <t>Assets/HotUpdateContent/Res/Map/14-9-9.asset</t>
+  </si>
+  <si>
+    <t>Assets/HotUpdateContent/Res/Map/15-9-9.asset</t>
+  </si>
+  <si>
+    <t>Assets/HotUpdateContent/Res/Map/17-9-9.asset</t>
+  </si>
+  <si>
+    <t>Assets/HotUpdateContent/Res/Map/18-9-9.asset</t>
+  </si>
+  <si>
+    <t>Assets/HotUpdateContent/Res/Map/19-9-9.asset</t>
+  </si>
+  <si>
+    <t>Assets/HotUpdateContent/Res/Map/10-10-10.asset</t>
+  </si>
+  <si>
+    <t>Assets/HotUpdateContent/Res/Map/12-10-10.asset</t>
+  </si>
+  <si>
+    <t>Assets/HotUpdateContent/Res/Map/13-10-10.asset</t>
+  </si>
+  <si>
+    <t>Assets/HotUpdateContent/Res/Map/14-10-10.asset</t>
+  </si>
+  <si>
+    <t>Assets/HotUpdateContent/Res/Map/15-10-10.asset</t>
+  </si>
+  <si>
+    <t>Assets/HotUpdateContent/Res/Map/16-10-10.asset</t>
+  </si>
+  <si>
+    <t>Assets/HotUpdateContent/Res/Map/17-10-10.asset</t>
+  </si>
+  <si>
+    <t>Assets/HotUpdateContent/Res/Map/18-10-10.asset</t>
+  </si>
+  <si>
+    <t>Assets/HotUpdateContent/Res/Map/19-10-10.asset</t>
+  </si>
+  <si>
+    <t>Assets/HotUpdateContent/Res/Map/4-10-10.asset</t>
+  </si>
+  <si>
+    <t>Assets/HotUpdateContent/Res/Map/6-10-10.asset</t>
+  </si>
+  <si>
+    <t>Assets/HotUpdateContent/Res/Map/7-10-10.asset</t>
+  </si>
+  <si>
+    <t>Assets/HotUpdateContent/Res/Map/8-10-10.asset</t>
+  </si>
+  <si>
+    <t>Assets/HotUpdateContent/Res/Map/10-11-11.asset</t>
+  </si>
+  <si>
+    <t>Assets/HotUpdateContent/Res/Map/12-11-11.asset</t>
+  </si>
+  <si>
+    <t>Assets/HotUpdateContent/Res/Map/13-11-11.asset</t>
+  </si>
+  <si>
+    <t>Assets/HotUpdateContent/Res/Map/14-11-11.asset</t>
+  </si>
+  <si>
+    <t>Assets/HotUpdateContent/Res/Map/15-11-11.asset</t>
+  </si>
+  <si>
+    <t>Assets/HotUpdateContent/Res/Map/16-11-11.asset</t>
+  </si>
+  <si>
+    <t>Assets/HotUpdateContent/Res/Map/17-11-11.asset</t>
+  </si>
+  <si>
+    <t>Assets/HotUpdateContent/Res/Map/18-11-11.asset</t>
+  </si>
+  <si>
+    <t>Assets/HotUpdateContent/Res/Map/19-11-11.asset</t>
+  </si>
+  <si>
+    <t>Assets/HotUpdateContent/Res/Map/4-11-11.asset</t>
+  </si>
+  <si>
+    <t>Assets/HotUpdateContent/Res/Map/6-11-11.asset</t>
+  </si>
+  <si>
+    <t>Assets/HotUpdateContent/Res/Map/7-11-11.asset</t>
+  </si>
+  <si>
+    <t>Assets/HotUpdateContent/Res/Map/8-11-11.asset</t>
+  </si>
+  <si>
+    <t>Assets/HotUpdateContent/Res/Map/10-12-12.asset</t>
+  </si>
+  <si>
+    <t>Assets/HotUpdateContent/Res/Map/12-12-12.asset</t>
+  </si>
+  <si>
+    <t>Assets/HotUpdateContent/Res/Map/13-12-12.asset</t>
+  </si>
+  <si>
+    <t>Assets/HotUpdateContent/Res/Map/14-12-12.asset</t>
+  </si>
+  <si>
+    <t>Assets/HotUpdateContent/Res/Map/15-12-12.asset</t>
+  </si>
+  <si>
+    <t>Assets/HotUpdateContent/Res/Map/16-12-12.asset</t>
+  </si>
+  <si>
+    <t>Assets/HotUpdateContent/Res/Map/17-12-12.asset</t>
+  </si>
+  <si>
+    <t>Assets/HotUpdateContent/Res/Map/18-12-12.asset</t>
+  </si>
+  <si>
+    <t>Assets/HotUpdateContent/Res/Map/19-12-12.asset</t>
+  </si>
+  <si>
+    <t>Assets/HotUpdateContent/Res/Map/4-12-12.asset</t>
+  </si>
+  <si>
+    <t>Assets/HotUpdateContent/Res/Map/5-12-12.asset</t>
+  </si>
+  <si>
+    <t>Assets/HotUpdateContent/Res/Map/6-12-12.asset</t>
+  </si>
+  <si>
+    <t>Assets/HotUpdateContent/Res/Map/7-12-12.asset</t>
+  </si>
+  <si>
+    <t>Assets/HotUpdateContent/Res/Map/8-12-12.asset</t>
+  </si>
+  <si>
+    <t>Assets/HotUpdateContent/Res/Map/10-13-13.asset</t>
+  </si>
+  <si>
+    <t>Assets/HotUpdateContent/Res/Map/12-13-13.asset</t>
+  </si>
+  <si>
+    <t>Assets/HotUpdateContent/Res/Map/13-13-13.asset</t>
+  </si>
+  <si>
+    <t>Assets/HotUpdateContent/Res/Map/14-13-13.asset</t>
+  </si>
+  <si>
+    <t>Assets/HotUpdateContent/Res/Map/15-13-13.asset</t>
+  </si>
+  <si>
+    <t>Assets/HotUpdateContent/Res/Map/16-13-13.asset</t>
+  </si>
+  <si>
+    <t>Assets/HotUpdateContent/Res/Map/17-13-13.asset</t>
+  </si>
+  <si>
+    <t>Assets/HotUpdateContent/Res/Map/18-13-13.asset</t>
+  </si>
+  <si>
+    <t>Assets/HotUpdateContent/Res/Map/19-13-13.asset</t>
+  </si>
+  <si>
+    <t>Assets/HotUpdateContent/Res/Map/4-13-13.asset</t>
+  </si>
+  <si>
+    <t>Assets/HotUpdateContent/Res/Map/6-13-13.asset</t>
+  </si>
+  <si>
+    <t>Assets/HotUpdateContent/Res/Map/7-13-13.asset</t>
+  </si>
+  <si>
+    <t>Assets/HotUpdateContent/Res/Map/8-13-13.asset</t>
+  </si>
+  <si>
+    <t>Assets/HotUpdateContent/Res/Map/9-13-13.asset</t>
+  </si>
+  <si>
+    <t>Assets/HotUpdateContent/Res/Map/10-14-14.asset</t>
+  </si>
+  <si>
+    <t>map_0001</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>map_009</t>
-  </si>
-  <si>
-    <t>map_010</t>
-  </si>
-  <si>
-    <t>map_011</t>
-  </si>
-  <si>
-    <t>map_012</t>
-  </si>
-  <si>
-    <t>map_013</t>
-  </si>
-  <si>
-    <t>map_014</t>
-  </si>
-  <si>
-    <t>map_015</t>
-  </si>
-  <si>
-    <t>map_016</t>
-  </si>
-  <si>
-    <t>map_017</t>
-  </si>
-  <si>
-    <t>map_018</t>
-  </si>
-  <si>
-    <t>map_019</t>
-  </si>
-  <si>
-    <t>map_020</t>
-  </si>
-  <si>
-    <t>map_021</t>
-  </si>
-  <si>
-    <t>map_022</t>
-  </si>
-  <si>
-    <t>map_023</t>
-  </si>
-  <si>
-    <t>map_024</t>
-  </si>
-  <si>
-    <t>Assets/HotUpdateContent/Res/Map/11-10-10.asset</t>
-  </si>
-  <si>
-    <t>Assets/HotUpdateContent/Res/Map/11-11-11.asset</t>
-  </si>
-  <si>
-    <t>Assets/HotUpdateContent/Res/Map/11-12-12.asset</t>
-  </si>
-  <si>
-    <t>Assets/HotUpdateContent/Res/Map/11-13-13.asset</t>
+    <t>map_0002</t>
+  </si>
+  <si>
+    <t>map_0003</t>
+  </si>
+  <si>
+    <t>map_0004</t>
+  </si>
+  <si>
+    <t>map_0005</t>
+  </si>
+  <si>
+    <t>map_0006</t>
+  </si>
+  <si>
+    <t>map_0007</t>
+  </si>
+  <si>
+    <t>map_0008</t>
+  </si>
+  <si>
+    <t>map_0009</t>
+  </si>
+  <si>
+    <t>map_0010</t>
+  </si>
+  <si>
+    <t>map_0011</t>
+  </si>
+  <si>
+    <t>map_0012</t>
+  </si>
+  <si>
+    <t>map_0013</t>
+  </si>
+  <si>
+    <t>map_0014</t>
+  </si>
+  <si>
+    <t>map_0015</t>
+  </si>
+  <si>
+    <t>map_0016</t>
+  </si>
+  <si>
+    <t>map_0017</t>
+  </si>
+  <si>
+    <t>map_0018</t>
+  </si>
+  <si>
+    <t>map_0019</t>
+  </si>
+  <si>
+    <t>map_0020</t>
+  </si>
+  <si>
+    <t>map_0021</t>
+  </si>
+  <si>
+    <t>map_0022</t>
+  </si>
+  <si>
+    <t>map_0023</t>
+  </si>
+  <si>
+    <t>map_0024</t>
+  </si>
+  <si>
+    <t>map_0025</t>
+  </si>
+  <si>
+    <t>map_0026</t>
+  </si>
+  <si>
+    <t>map_0027</t>
+  </si>
+  <si>
+    <t>map_0028</t>
+  </si>
+  <si>
+    <t>map_0029</t>
+  </si>
+  <si>
+    <t>map_0030</t>
+  </si>
+  <si>
+    <t>map_0031</t>
+  </si>
+  <si>
+    <t>map_0032</t>
+  </si>
+  <si>
+    <t>map_0033</t>
+  </si>
+  <si>
+    <t>map_0034</t>
+  </si>
+  <si>
+    <t>map_0035</t>
+  </si>
+  <si>
+    <t>map_0036</t>
+  </si>
+  <si>
+    <t>map_0037</t>
+  </si>
+  <si>
+    <t>map_0038</t>
+  </si>
+  <si>
+    <t>map_0039</t>
+  </si>
+  <si>
+    <t>map_0040</t>
+  </si>
+  <si>
+    <t>map_0041</t>
+  </si>
+  <si>
+    <t>map_0042</t>
+  </si>
+  <si>
+    <t>map_0043</t>
+  </si>
+  <si>
+    <t>map_0044</t>
+  </si>
+  <si>
+    <t>map_0045</t>
+  </si>
+  <si>
+    <t>map_0046</t>
+  </si>
+  <si>
+    <t>map_0047</t>
+  </si>
+  <si>
+    <t>map_0048</t>
+  </si>
+  <si>
+    <t>map_0049</t>
+  </si>
+  <si>
+    <t>map_0050</t>
+  </si>
+  <si>
+    <t>map_0051</t>
+  </si>
+  <si>
+    <t>map_0052</t>
+  </si>
+  <si>
+    <t>map_0053</t>
+  </si>
+  <si>
+    <t>map_0054</t>
+  </si>
+  <si>
+    <t>map_0055</t>
+  </si>
+  <si>
+    <t>map_0056</t>
+  </si>
+  <si>
+    <t>map_0057</t>
+  </si>
+  <si>
+    <t>map_0058</t>
+  </si>
+  <si>
+    <t>map_0059</t>
+  </si>
+  <si>
+    <t>map_0060</t>
+  </si>
+  <si>
+    <t>map_0061</t>
+  </si>
+  <si>
+    <t>map_0062</t>
+  </si>
+  <si>
+    <t>map_0063</t>
+  </si>
+  <si>
+    <t>map_0064</t>
+  </si>
+  <si>
+    <t>map_0065</t>
+  </si>
+  <si>
+    <t>map_0066</t>
+  </si>
+  <si>
+    <t>map_0067</t>
+  </si>
+  <si>
+    <t>map_0068</t>
+  </si>
+  <si>
+    <t>map_0069</t>
+  </si>
+  <si>
+    <t>map_0070</t>
+  </si>
+  <si>
+    <t>map_0071</t>
+  </si>
+  <si>
+    <t>map_0072</t>
+  </si>
+  <si>
+    <t>map_1001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>map_1002</t>
+  </si>
+  <si>
+    <t>map_1003</t>
+  </si>
+  <si>
+    <t>map_1004</t>
+  </si>
+  <si>
+    <t>map_1005</t>
+  </si>
+  <si>
+    <t>map_1006</t>
+  </si>
+  <si>
+    <t>map_1007</t>
+  </si>
+  <si>
+    <t>map_1008</t>
+  </si>
+  <si>
+    <t>map_1009</t>
+  </si>
+  <si>
+    <t>map_1010</t>
+  </si>
+  <si>
+    <t>map_1011</t>
+  </si>
+  <si>
+    <t>map_1012</t>
+  </si>
+  <si>
+    <t>map_1013</t>
+  </si>
+  <si>
+    <t>map_1014</t>
+  </si>
+  <si>
+    <t>map_1015</t>
+  </si>
+  <si>
+    <t>map_1016</t>
+  </si>
+  <si>
+    <t>map_1017</t>
+  </si>
+  <si>
+    <t>map_1018</t>
+  </si>
+  <si>
+    <t>map_1019</t>
+  </si>
+  <si>
+    <t>map_1020</t>
+  </si>
+  <si>
+    <t>map_1021</t>
+  </si>
+  <si>
+    <t>map_1022</t>
+  </si>
+  <si>
+    <t>map_1023</t>
+  </si>
+  <si>
+    <t>map_1024</t>
+  </si>
+  <si>
+    <t>map_1025</t>
+  </si>
+  <si>
+    <t>map_1026</t>
+  </si>
+  <si>
+    <t>map_1027</t>
+  </si>
+  <si>
+    <t>map_1028</t>
+  </si>
+  <si>
+    <t>map_1029</t>
+  </si>
+  <si>
+    <t>map_1030</t>
+  </si>
+  <si>
+    <t>map_1031</t>
+  </si>
+  <si>
+    <t>map_1032</t>
+  </si>
+  <si>
+    <t>map_1033</t>
+  </si>
+  <si>
+    <t>map_1034</t>
+  </si>
+  <si>
+    <t>map_1035</t>
+  </si>
+  <si>
+    <t>map_1036</t>
+  </si>
+  <si>
+    <t>map_1037</t>
+  </si>
+  <si>
+    <t>map_1038</t>
+  </si>
+  <si>
+    <t>map_1039</t>
+  </si>
+  <si>
+    <t>map_1040</t>
+  </si>
+  <si>
+    <t>map_1041</t>
+  </si>
+  <si>
+    <t>map_1042</t>
+  </si>
+  <si>
+    <t>map_1043</t>
+  </si>
+  <si>
+    <t>map_1044</t>
+  </si>
+  <si>
+    <t>map_1045</t>
+  </si>
+  <si>
+    <t>map_1046</t>
+  </si>
+  <si>
+    <t>map_1047</t>
+  </si>
+  <si>
+    <t>map_1048</t>
+  </si>
+  <si>
+    <t>map_1049</t>
+  </si>
+  <si>
+    <t>map_1050</t>
+  </si>
+  <si>
+    <t>map_1051</t>
+  </si>
+  <si>
+    <t>map_1052</t>
+  </si>
+  <si>
+    <t>map_1053</t>
+  </si>
+  <si>
+    <t>map_1054</t>
+  </si>
+  <si>
+    <t>map_1055</t>
+  </si>
+  <si>
+    <t>map_1056</t>
+  </si>
+  <si>
+    <t>map_1057</t>
+  </si>
+  <si>
+    <t>map_1058</t>
+  </si>
+  <si>
+    <t>map_1059</t>
+  </si>
+  <si>
+    <t>map_1060</t>
+  </si>
+  <si>
+    <t>map_1061</t>
+  </si>
+  <si>
+    <t>map_1062</t>
+  </si>
+  <si>
+    <t>map_1063</t>
+  </si>
+  <si>
+    <t>map_1064</t>
+  </si>
+  <si>
+    <t>map_1065</t>
+  </si>
+  <si>
+    <t>map_1066</t>
+  </si>
+  <si>
+    <t>map_1067</t>
+  </si>
+  <si>
+    <t>map_1068</t>
+  </si>
+  <si>
+    <t>map_1069</t>
+  </si>
+  <si>
+    <t>map_1070</t>
+  </si>
+  <si>
+    <t>map_1071</t>
+  </si>
+  <si>
+    <t>map_1072</t>
+  </si>
+  <si>
+    <t>map_2001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>map_2002</t>
+  </si>
+  <si>
+    <t>map_2003</t>
+  </si>
+  <si>
+    <t>map_2004</t>
+  </si>
+  <si>
+    <t>map_2005</t>
+  </si>
+  <si>
+    <t>map_2006</t>
+  </si>
+  <si>
+    <t>map_2007</t>
+  </si>
+  <si>
+    <t>map_2008</t>
+  </si>
+  <si>
+    <t>map_2009</t>
+  </si>
+  <si>
+    <t>map_2010</t>
+  </si>
+  <si>
+    <t>map_2011</t>
+  </si>
+  <si>
+    <t>map_2012</t>
+  </si>
+  <si>
+    <t>map_2013</t>
+  </si>
+  <si>
+    <t>map_2014</t>
+  </si>
+  <si>
+    <t>map_2015</t>
+  </si>
+  <si>
+    <t>map_2016</t>
+  </si>
+  <si>
+    <t>map_2017</t>
+  </si>
+  <si>
+    <t>map_2018</t>
+  </si>
+  <si>
+    <t>map_2019</t>
+  </si>
+  <si>
+    <t>map_2020</t>
+  </si>
+  <si>
+    <t>map_2021</t>
+  </si>
+  <si>
+    <t>map_2022</t>
+  </si>
+  <si>
+    <t>map_2023</t>
+  </si>
+  <si>
+    <t>map_2024</t>
+  </si>
+  <si>
+    <t>map_2025</t>
+  </si>
+  <si>
+    <t>map_2026</t>
+  </si>
+  <si>
+    <t>map_2027</t>
+  </si>
+  <si>
+    <t>map_2028</t>
+  </si>
+  <si>
+    <t>map_2029</t>
+  </si>
+  <si>
+    <t>map_2030</t>
+  </si>
+  <si>
+    <t>map_2031</t>
+  </si>
+  <si>
+    <t>map_2032</t>
+  </si>
+  <si>
+    <t>map_2033</t>
+  </si>
+  <si>
+    <t>map_2034</t>
+  </si>
+  <si>
+    <t>map_2035</t>
+  </si>
+  <si>
+    <t>map_2036</t>
+  </si>
+  <si>
+    <t>map_2037</t>
+  </si>
+  <si>
+    <t>map_2038</t>
+  </si>
+  <si>
+    <t>map_2039</t>
+  </si>
+  <si>
+    <t>map_2040</t>
+  </si>
+  <si>
+    <t>map_2041</t>
+  </si>
+  <si>
+    <t>map_2042</t>
+  </si>
+  <si>
+    <t>map_2043</t>
+  </si>
+  <si>
+    <t>map_2044</t>
+  </si>
+  <si>
+    <t>map_2045</t>
+  </si>
+  <si>
+    <t>map_2046</t>
+  </si>
+  <si>
+    <t>map_2047</t>
+  </si>
+  <si>
+    <t>map_2048</t>
+  </si>
+  <si>
+    <t>map_2049</t>
+  </si>
+  <si>
+    <t>map_2050</t>
+  </si>
+  <si>
+    <t>map_2051</t>
+  </si>
+  <si>
+    <t>map_2052</t>
+  </si>
+  <si>
+    <t>map_2053</t>
+  </si>
+  <si>
+    <t>map_2054</t>
+  </si>
+  <si>
+    <t>map_2055</t>
+  </si>
+  <si>
+    <t>map_2056</t>
+  </si>
+  <si>
+    <t>map_2057</t>
+  </si>
+  <si>
+    <t>map_2058</t>
+  </si>
+  <si>
+    <t>map_2059</t>
+  </si>
+  <si>
+    <t>map_2060</t>
+  </si>
+  <si>
+    <t>map_2061</t>
+  </si>
+  <si>
+    <t>map_2062</t>
+  </si>
+  <si>
+    <t>map_2063</t>
+  </si>
+  <si>
+    <t>map_2064</t>
+  </si>
+  <si>
+    <t>map_2065</t>
+  </si>
+  <si>
+    <t>map_2066</t>
+  </si>
+  <si>
+    <t>map_2067</t>
+  </si>
+  <si>
+    <t>map_2068</t>
+  </si>
+  <si>
+    <t>map_2069</t>
+  </si>
+  <si>
+    <t>map_2070</t>
+  </si>
+  <si>
+    <t>map_2071</t>
+  </si>
+  <si>
+    <t>map_2072</t>
+  </si>
+  <si>
+    <t>map_3001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>map_3002</t>
+  </si>
+  <si>
+    <t>map_3003</t>
+  </si>
+  <si>
+    <t>map_3004</t>
+  </si>
+  <si>
+    <t>map_3005</t>
+  </si>
+  <si>
+    <t>map_3006</t>
+  </si>
+  <si>
+    <t>map_3007</t>
+  </si>
+  <si>
+    <t>map_3008</t>
+  </si>
+  <si>
+    <t>map_3009</t>
+  </si>
+  <si>
+    <t>map_3010</t>
+  </si>
+  <si>
+    <t>map_3011</t>
+  </si>
+  <si>
+    <t>map_3012</t>
+  </si>
+  <si>
+    <t>map_3013</t>
+  </si>
+  <si>
+    <t>map_3014</t>
+  </si>
+  <si>
+    <t>map_3015</t>
+  </si>
+  <si>
+    <t>map_3016</t>
+  </si>
+  <si>
+    <t>map_3017</t>
+  </si>
+  <si>
+    <t>map_3018</t>
+  </si>
+  <si>
+    <t>map_3019</t>
+  </si>
+  <si>
+    <t>map_3020</t>
+  </si>
+  <si>
+    <t>map_3021</t>
+  </si>
+  <si>
+    <t>map_3022</t>
+  </si>
+  <si>
+    <t>map_3023</t>
+  </si>
+  <si>
+    <t>map_3024</t>
+  </si>
+  <si>
+    <t>map_3025</t>
+  </si>
+  <si>
+    <t>map_3026</t>
+  </si>
+  <si>
+    <t>map_3027</t>
+  </si>
+  <si>
+    <t>map_3028</t>
+  </si>
+  <si>
+    <t>map_3029</t>
+  </si>
+  <si>
+    <t>map_3030</t>
+  </si>
+  <si>
+    <t>map_3031</t>
+  </si>
+  <si>
+    <t>map_3032</t>
+  </si>
+  <si>
+    <t>map_3033</t>
+  </si>
+  <si>
+    <t>map_3034</t>
+  </si>
+  <si>
+    <t>map_3035</t>
+  </si>
+  <si>
+    <t>map_3036</t>
+  </si>
+  <si>
+    <t>map_3037</t>
+  </si>
+  <si>
+    <t>map_3038</t>
+  </si>
+  <si>
+    <t>map_3039</t>
+  </si>
+  <si>
+    <t>map_3040</t>
+  </si>
+  <si>
+    <t>map_3041</t>
+  </si>
+  <si>
+    <t>map_3042</t>
+  </si>
+  <si>
+    <t>map_3043</t>
+  </si>
+  <si>
+    <t>map_3044</t>
+  </si>
+  <si>
+    <t>map_3045</t>
+  </si>
+  <si>
+    <t>map_3046</t>
+  </si>
+  <si>
+    <t>map_3047</t>
+  </si>
+  <si>
+    <t>map_3048</t>
+  </si>
+  <si>
+    <t>map_3049</t>
+  </si>
+  <si>
+    <t>map_3050</t>
+  </si>
+  <si>
+    <t>map_3051</t>
+  </si>
+  <si>
+    <t>map_3052</t>
+  </si>
+  <si>
+    <t>map_3053</t>
+  </si>
+  <si>
+    <t>map_3054</t>
+  </si>
+  <si>
+    <t>map_3055</t>
+  </si>
+  <si>
+    <t>map_3056</t>
+  </si>
+  <si>
+    <t>map_3057</t>
+  </si>
+  <si>
+    <t>map_3058</t>
+  </si>
+  <si>
+    <t>map_3059</t>
+  </si>
+  <si>
+    <t>map_3060</t>
+  </si>
+  <si>
+    <t>map_3061</t>
+  </si>
+  <si>
+    <t>map_3062</t>
+  </si>
+  <si>
+    <t>map_3063</t>
+  </si>
+  <si>
+    <t>map_3064</t>
+  </si>
+  <si>
+    <t>map_3065</t>
+  </si>
+  <si>
+    <t>map_3066</t>
+  </si>
+  <si>
+    <t>map_3067</t>
+  </si>
+  <si>
+    <t>map_3068</t>
+  </si>
+  <si>
+    <t>map_3069</t>
+  </si>
+  <si>
+    <t>map_3070</t>
+  </si>
+  <si>
+    <t>map_3071</t>
+  </si>
+  <si>
+    <t>map_3072</t>
   </si>
 </sst>
 </file>
@@ -576,11 +1569,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{537D5B2F-D815-43F0-9E00-860E54D6EE48}">
-  <dimension ref="A1:D26"/>
+  <dimension ref="A1:D290"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="8.5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="42.58203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="48.08203125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="16" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="15.9140625" bestFit="1" customWidth="1"/>
   </cols>
@@ -615,10 +1608,10 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>8</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>11</v>
       </c>
       <c r="C3" s="3">
         <v>11</v>
@@ -628,329 +1621,4026 @@
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A4" s="4" t="s">
-        <v>9</v>
+      <c r="A4" s="1" t="s">
+        <v>81</v>
       </c>
       <c r="B4" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4" s="3">
         <v>11</v>
       </c>
-      <c r="C4" s="6">
+      <c r="D4" s="2">
         <v>14</v>
-      </c>
-      <c r="D4" s="5">
-        <v>16</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
-        <v>10</v>
+        <v>82</v>
       </c>
       <c r="B5" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C5" s="3">
         <v>11</v>
       </c>
-      <c r="C5" s="3">
-        <v>16</v>
-      </c>
       <c r="D5" s="2">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
-        <v>12</v>
+        <v>83</v>
       </c>
       <c r="B6" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C6" s="3">
         <v>11</v>
       </c>
-      <c r="C6" s="3">
-        <v>17</v>
-      </c>
       <c r="D6" s="2">
-        <v>19</v>
+        <v>14</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
-        <v>13</v>
+        <v>84</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C7" s="3">
+        <v>11</v>
+      </c>
+      <c r="D7" s="2">
         <v>14</v>
-      </c>
-      <c r="D7" s="2">
-        <v>17</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
-        <v>14</v>
+        <v>85</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C8" s="6">
-        <v>17</v>
-      </c>
-      <c r="D8" s="5">
-        <v>20</v>
+      <c r="C8" s="3">
+        <v>11</v>
+      </c>
+      <c r="D8" s="2">
+        <v>14</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
-        <v>15</v>
+        <v>86</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C9" s="3">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="D9" s="2">
-        <v>22</v>
+        <v>14</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
-        <v>16</v>
+        <v>87</v>
       </c>
       <c r="B10" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C10" s="3">
+        <v>14</v>
+      </c>
+      <c r="D10" s="2">
         <v>17</v>
-      </c>
-      <c r="C10" s="3">
-        <v>22</v>
-      </c>
-      <c r="D10" s="2">
-        <v>24</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
-        <v>18</v>
+        <v>88</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="C11" s="3">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="D11" s="2">
-        <v>22</v>
+        <v>17</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
-        <v>19</v>
+        <v>89</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="C12" s="6">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="D12" s="5">
-        <v>25</v>
+        <v>17</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
-        <v>20</v>
+        <v>90</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="C13" s="3">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="D13" s="2">
-        <v>28</v>
+        <v>17</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="C14" s="3">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="D14" s="2">
-        <v>30</v>
+        <v>17</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
-        <v>22</v>
+        <v>92</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="C15" s="3">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="D15" s="2">
-        <v>26</v>
+        <v>17</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
-        <v>23</v>
+        <v>93</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="C16" s="6">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="D16" s="5">
-        <v>30</v>
+        <v>22</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
-        <v>24</v>
+        <v>94</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>35</v>
+        <v>9</v>
       </c>
       <c r="C17" s="3">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="D17" s="2">
-        <v>33</v>
+        <v>22</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
-        <v>25</v>
+        <v>95</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="C18" s="3">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="D18" s="2">
-        <v>36</v>
+        <v>22</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
-        <v>26</v>
+        <v>96</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="C19" s="3">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="D19" s="2">
-        <v>31</v>
+        <v>22</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
-        <v>27</v>
+        <v>97</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="C20" s="6">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="D20" s="5">
-        <v>36</v>
+        <v>22</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
-        <v>28</v>
+        <v>98</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="C21" s="3">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="D21" s="2">
-        <v>40</v>
+        <v>22</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
-        <v>29</v>
+        <v>99</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="C22" s="3">
-        <v>40</v>
+        <v>18</v>
       </c>
       <c r="D22" s="2">
-        <v>43</v>
+        <v>22</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
-        <v>30</v>
+        <v>100</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="C23" s="3">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="D23" s="2">
-        <v>37</v>
+        <v>22</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
-        <v>31</v>
+        <v>101</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="C24" s="6">
-        <v>37</v>
+        <v>18</v>
       </c>
       <c r="D24" s="5">
-        <v>42</v>
+        <v>22</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
-        <v>32</v>
+        <v>102</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="C25" s="3">
-        <v>42</v>
+        <v>18</v>
       </c>
       <c r="D25" s="2">
-        <v>47</v>
+        <v>22</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C26" s="3">
+        <v>18</v>
+      </c>
+      <c r="D26" s="2">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A27" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="B27" t="s">
+        <v>35</v>
+      </c>
+      <c r="C27">
+        <v>18</v>
+      </c>
+      <c r="D27">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A28" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="B28" t="s">
+        <v>36</v>
+      </c>
+      <c r="C28">
+        <v>18</v>
+      </c>
+      <c r="D28">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A29" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="B29" t="s">
+        <v>37</v>
+      </c>
+      <c r="C29">
+        <v>18</v>
+      </c>
+      <c r="D29">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A30" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="B30" t="s">
+        <v>38</v>
+      </c>
+      <c r="C30">
+        <v>21</v>
+      </c>
+      <c r="D30">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A31" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="B31" t="s">
+        <v>10</v>
+      </c>
+      <c r="C31">
+        <v>21</v>
+      </c>
+      <c r="D31">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A32" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="B32" t="s">
+        <v>39</v>
+      </c>
+      <c r="C32">
+        <v>21</v>
+      </c>
+      <c r="D32">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A33" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="B33" t="s">
+        <v>40</v>
+      </c>
+      <c r="C33">
+        <v>21</v>
+      </c>
+      <c r="D33">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A34" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="B34" t="s">
+        <v>41</v>
+      </c>
+      <c r="C34">
+        <v>21</v>
+      </c>
+      <c r="D34">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A35" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="B35" t="s">
+        <v>42</v>
+      </c>
+      <c r="C35">
+        <v>21</v>
+      </c>
+      <c r="D35">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A36" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="B36" t="s">
+        <v>43</v>
+      </c>
+      <c r="C36">
+        <v>21</v>
+      </c>
+      <c r="D36">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A37" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="B37" t="s">
+        <v>44</v>
+      </c>
+      <c r="C37">
+        <v>21</v>
+      </c>
+      <c r="D37">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A38" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B38" t="s">
+        <v>45</v>
+      </c>
+      <c r="C38">
+        <v>21</v>
+      </c>
+      <c r="D38">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A39" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="B39" t="s">
+        <v>46</v>
+      </c>
+      <c r="C39">
+        <v>21</v>
+      </c>
+      <c r="D39">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A40" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="B40" t="s">
+        <v>47</v>
+      </c>
+      <c r="C40">
+        <v>21</v>
+      </c>
+      <c r="D40">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A41" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="B41" t="s">
+        <v>48</v>
+      </c>
+      <c r="C41">
+        <v>21</v>
+      </c>
+      <c r="D41">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A42" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="B42" t="s">
+        <v>49</v>
+      </c>
+      <c r="C42">
+        <v>21</v>
+      </c>
+      <c r="D42">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A43" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="B43" t="s">
+        <v>50</v>
+      </c>
+      <c r="C43">
+        <v>21</v>
+      </c>
+      <c r="D43">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A44" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="B44" t="s">
+        <v>51</v>
+      </c>
+      <c r="C44">
+        <v>25</v>
+      </c>
+      <c r="D44">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A45" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="B45" t="s">
+        <v>11</v>
+      </c>
+      <c r="C45">
+        <v>25</v>
+      </c>
+      <c r="D45">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A46" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="B46" t="s">
+        <v>52</v>
+      </c>
+      <c r="C46">
+        <v>25</v>
+      </c>
+      <c r="D46">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A47" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="B47" t="s">
+        <v>53</v>
+      </c>
+      <c r="C47">
+        <v>25</v>
+      </c>
+      <c r="D47">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A48" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="B48" t="s">
+        <v>54</v>
+      </c>
+      <c r="C48">
+        <v>25</v>
+      </c>
+      <c r="D48">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A49" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="B49" t="s">
+        <v>55</v>
+      </c>
+      <c r="C49">
+        <v>25</v>
+      </c>
+      <c r="D49">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A50" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="B50" t="s">
+        <v>56</v>
+      </c>
+      <c r="C50">
+        <v>25</v>
+      </c>
+      <c r="D50">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A51" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="B51" t="s">
+        <v>57</v>
+      </c>
+      <c r="C51">
+        <v>25</v>
+      </c>
+      <c r="D51">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A52" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="B52" t="s">
+        <v>58</v>
+      </c>
+      <c r="C52">
+        <v>25</v>
+      </c>
+      <c r="D52">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A53" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="B53" t="s">
+        <v>59</v>
+      </c>
+      <c r="C53">
+        <v>25</v>
+      </c>
+      <c r="D53">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A54" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="B54" t="s">
+        <v>60</v>
+      </c>
+      <c r="C54">
+        <v>25</v>
+      </c>
+      <c r="D54">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A55" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="B55" t="s">
+        <v>61</v>
+      </c>
+      <c r="C55">
+        <v>25</v>
+      </c>
+      <c r="D55">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A56" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="B56" t="s">
+        <v>62</v>
+      </c>
+      <c r="C56">
+        <v>25</v>
+      </c>
+      <c r="D56">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A57" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="B57" t="s">
+        <v>63</v>
+      </c>
+      <c r="C57">
+        <v>25</v>
+      </c>
+      <c r="D57">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A58" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="B58" t="s">
+        <v>64</v>
+      </c>
+      <c r="C58">
+        <v>25</v>
+      </c>
+      <c r="D58">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A59" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="B59" t="s">
+        <v>65</v>
+      </c>
+      <c r="C59">
+        <v>30</v>
+      </c>
+      <c r="D59">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A60" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="B60" t="s">
+        <v>12</v>
+      </c>
+      <c r="C60">
+        <v>30</v>
+      </c>
+      <c r="D60">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A61" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="B61" t="s">
+        <v>66</v>
+      </c>
+      <c r="C61">
+        <v>30</v>
+      </c>
+      <c r="D61">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A62" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="B62" t="s">
+        <v>67</v>
+      </c>
+      <c r="C62">
+        <v>30</v>
+      </c>
+      <c r="D62">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A63" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="B63" t="s">
+        <v>68</v>
+      </c>
+      <c r="C63">
+        <v>30</v>
+      </c>
+      <c r="D63">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A64" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="B64" t="s">
+        <v>69</v>
+      </c>
+      <c r="C64">
+        <v>30</v>
+      </c>
+      <c r="D64">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A65" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="B65" t="s">
+        <v>70</v>
+      </c>
+      <c r="C65">
+        <v>30</v>
+      </c>
+      <c r="D65">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A66" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="B66" t="s">
+        <v>71</v>
+      </c>
+      <c r="C66">
+        <v>30</v>
+      </c>
+      <c r="D66">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A67" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B67" t="s">
+        <v>72</v>
+      </c>
+      <c r="C67">
+        <v>30</v>
+      </c>
+      <c r="D67">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A68" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="B68" t="s">
+        <v>73</v>
+      </c>
+      <c r="C68">
+        <v>30</v>
+      </c>
+      <c r="D68">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A69" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="B69" t="s">
+        <v>74</v>
+      </c>
+      <c r="C69">
+        <v>30</v>
+      </c>
+      <c r="D69">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A70" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="B70" t="s">
+        <v>75</v>
+      </c>
+      <c r="C70">
+        <v>30</v>
+      </c>
+      <c r="D70">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A71" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="B71" t="s">
+        <v>76</v>
+      </c>
+      <c r="C71">
+        <v>30</v>
+      </c>
+      <c r="D71">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A72" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="B72" t="s">
+        <v>77</v>
+      </c>
+      <c r="C72">
+        <v>30</v>
+      </c>
+      <c r="D72">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A73" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="B73" t="s">
+        <v>78</v>
+      </c>
+      <c r="C73">
+        <v>30</v>
+      </c>
+      <c r="D73">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A74" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="B74" t="s">
+        <v>79</v>
+      </c>
+      <c r="C74">
+        <v>35</v>
+      </c>
+      <c r="D74">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A75" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="B75" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C75">
+        <v>14</v>
+      </c>
+      <c r="D75">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A76" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="B76" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C76">
+        <v>14</v>
+      </c>
+      <c r="D76">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A77" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="B77" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C77">
+        <v>14</v>
+      </c>
+      <c r="D77">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A78" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="B78" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C78">
+        <v>14</v>
+      </c>
+      <c r="D78">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A79" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="B79" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C79">
+        <v>14</v>
+      </c>
+      <c r="D79">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A80" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="B80" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C80">
+        <v>14</v>
+      </c>
+      <c r="D80">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A81" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="B81" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C81">
+        <v>14</v>
+      </c>
+      <c r="D81">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A82" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="B82" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C82">
+        <v>17</v>
+      </c>
+      <c r="D82">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A83" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="B83" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C83">
+        <v>17</v>
+      </c>
+      <c r="D83">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A84" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="B84" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C84">
+        <v>17</v>
+      </c>
+      <c r="D84">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A85" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="B85" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C85">
+        <v>17</v>
+      </c>
+      <c r="D85">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A86" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="B86" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C86">
+        <v>17</v>
+      </c>
+      <c r="D86">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="87" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A87" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="B87" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C87">
+        <v>17</v>
+      </c>
+      <c r="D87">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="88" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A88" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="B88" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C88">
+        <v>22</v>
+      </c>
+      <c r="D88">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="89" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A89" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="B89" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C89">
+        <v>22</v>
+      </c>
+      <c r="D89">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="90" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A90" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="B90" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C90">
+        <v>22</v>
+      </c>
+      <c r="D90">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="91" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A91" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="B91" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C91">
+        <v>22</v>
+      </c>
+      <c r="D91">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="92" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A92" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="B92" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C92">
+        <v>22</v>
+      </c>
+      <c r="D92">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="93" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A93" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="B93" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C93">
+        <v>22</v>
+      </c>
+      <c r="D93">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="94" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A94" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="B94" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C94">
+        <v>22</v>
+      </c>
+      <c r="D94">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="95" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A95" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="B95" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C95">
+        <v>22</v>
+      </c>
+      <c r="D95">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="96" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A96" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="B96" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C96">
+        <v>22</v>
+      </c>
+      <c r="D96">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="97" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A97" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="B97" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="B26" s="2" t="s">
+      <c r="C97">
+        <v>22</v>
+      </c>
+      <c r="D97">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="98" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A98" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="B98" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C98">
+        <v>22</v>
+      </c>
+      <c r="D98">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="99" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A99" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="B99" t="s">
+        <v>35</v>
+      </c>
+      <c r="C99">
+        <v>22</v>
+      </c>
+      <c r="D99">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="100" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A100" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="B100" t="s">
+        <v>36</v>
+      </c>
+      <c r="C100">
+        <v>22</v>
+      </c>
+      <c r="D100">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="101" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A101" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="B101" t="s">
         <v>37</v>
       </c>
-      <c r="C26" s="3">
+      <c r="C101">
+        <v>22</v>
+      </c>
+      <c r="D101">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="102" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A102" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="B102" t="s">
+        <v>38</v>
+      </c>
+      <c r="C102">
+        <v>26</v>
+      </c>
+      <c r="D102">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="103" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A103" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="B103" t="s">
+        <v>10</v>
+      </c>
+      <c r="C103">
+        <v>26</v>
+      </c>
+      <c r="D103">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="104" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A104" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="B104" t="s">
+        <v>39</v>
+      </c>
+      <c r="C104">
+        <v>26</v>
+      </c>
+      <c r="D104">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="105" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A105" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="B105" t="s">
+        <v>40</v>
+      </c>
+      <c r="C105">
+        <v>26</v>
+      </c>
+      <c r="D105">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="106" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A106" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="B106" t="s">
+        <v>41</v>
+      </c>
+      <c r="C106">
+        <v>26</v>
+      </c>
+      <c r="D106">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="107" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A107" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="B107" t="s">
+        <v>42</v>
+      </c>
+      <c r="C107">
+        <v>26</v>
+      </c>
+      <c r="D107">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="108" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A108" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="B108" t="s">
+        <v>43</v>
+      </c>
+      <c r="C108">
+        <v>26</v>
+      </c>
+      <c r="D108">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="109" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A109" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="B109" t="s">
+        <v>44</v>
+      </c>
+      <c r="C109">
+        <v>26</v>
+      </c>
+      <c r="D109">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="110" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A110" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="B110" t="s">
+        <v>45</v>
+      </c>
+      <c r="C110">
+        <v>26</v>
+      </c>
+      <c r="D110">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="111" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A111" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="B111" t="s">
+        <v>46</v>
+      </c>
+      <c r="C111">
+        <v>26</v>
+      </c>
+      <c r="D111">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="112" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A112" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="B112" t="s">
         <v>47</v>
       </c>
-      <c r="D26" s="2">
+      <c r="C112">
+        <v>26</v>
+      </c>
+      <c r="D112">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="113" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A113" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="B113" t="s">
+        <v>48</v>
+      </c>
+      <c r="C113">
+        <v>26</v>
+      </c>
+      <c r="D113">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="114" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A114" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="B114" t="s">
+        <v>49</v>
+      </c>
+      <c r="C114">
+        <v>26</v>
+      </c>
+      <c r="D114">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="115" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A115" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="B115" t="s">
         <v>50</v>
+      </c>
+      <c r="C115">
+        <v>26</v>
+      </c>
+      <c r="D115">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="116" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A116" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="B116" t="s">
+        <v>51</v>
+      </c>
+      <c r="C116">
+        <v>31</v>
+      </c>
+      <c r="D116">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="117" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A117" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="B117" t="s">
+        <v>11</v>
+      </c>
+      <c r="C117">
+        <v>31</v>
+      </c>
+      <c r="D117">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="118" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A118" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="B118" t="s">
+        <v>52</v>
+      </c>
+      <c r="C118">
+        <v>31</v>
+      </c>
+      <c r="D118">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="119" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A119" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="B119" t="s">
+        <v>53</v>
+      </c>
+      <c r="C119">
+        <v>31</v>
+      </c>
+      <c r="D119">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="120" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A120" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="B120" t="s">
+        <v>54</v>
+      </c>
+      <c r="C120">
+        <v>31</v>
+      </c>
+      <c r="D120">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="121" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A121" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="B121" t="s">
+        <v>55</v>
+      </c>
+      <c r="C121">
+        <v>31</v>
+      </c>
+      <c r="D121">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="122" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A122" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="B122" t="s">
+        <v>56</v>
+      </c>
+      <c r="C122">
+        <v>31</v>
+      </c>
+      <c r="D122">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="123" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A123" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="B123" t="s">
+        <v>57</v>
+      </c>
+      <c r="C123">
+        <v>31</v>
+      </c>
+      <c r="D123">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="124" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A124" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="B124" t="s">
+        <v>58</v>
+      </c>
+      <c r="C124">
+        <v>31</v>
+      </c>
+      <c r="D124">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="125" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A125" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="B125" t="s">
+        <v>59</v>
+      </c>
+      <c r="C125">
+        <v>31</v>
+      </c>
+      <c r="D125">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="126" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A126" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="B126" t="s">
+        <v>60</v>
+      </c>
+      <c r="C126">
+        <v>31</v>
+      </c>
+      <c r="D126">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="127" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A127" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="B127" t="s">
+        <v>61</v>
+      </c>
+      <c r="C127">
+        <v>31</v>
+      </c>
+      <c r="D127">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="128" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A128" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="B128" t="s">
+        <v>62</v>
+      </c>
+      <c r="C128">
+        <v>31</v>
+      </c>
+      <c r="D128">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="129" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A129" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="B129" t="s">
+        <v>63</v>
+      </c>
+      <c r="C129">
+        <v>31</v>
+      </c>
+      <c r="D129">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="130" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A130" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="B130" t="s">
+        <v>64</v>
+      </c>
+      <c r="C130">
+        <v>31</v>
+      </c>
+      <c r="D130">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="131" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A131" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="B131" t="s">
+        <v>65</v>
+      </c>
+      <c r="C131">
+        <v>37</v>
+      </c>
+      <c r="D131">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="132" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A132" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="B132" t="s">
+        <v>12</v>
+      </c>
+      <c r="C132">
+        <v>37</v>
+      </c>
+      <c r="D132">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="133" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A133" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="B133" t="s">
+        <v>66</v>
+      </c>
+      <c r="C133">
+        <v>37</v>
+      </c>
+      <c r="D133">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="134" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A134" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="B134" t="s">
+        <v>67</v>
+      </c>
+      <c r="C134">
+        <v>37</v>
+      </c>
+      <c r="D134">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="135" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A135" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="B135" t="s">
+        <v>68</v>
+      </c>
+      <c r="C135">
+        <v>37</v>
+      </c>
+      <c r="D135">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="136" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A136" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="B136" t="s">
+        <v>69</v>
+      </c>
+      <c r="C136">
+        <v>37</v>
+      </c>
+      <c r="D136">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="137" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A137" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="B137" t="s">
+        <v>70</v>
+      </c>
+      <c r="C137">
+        <v>37</v>
+      </c>
+      <c r="D137">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="138" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A138" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="B138" t="s">
+        <v>71</v>
+      </c>
+      <c r="C138">
+        <v>37</v>
+      </c>
+      <c r="D138">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="139" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A139" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="B139" t="s">
+        <v>72</v>
+      </c>
+      <c r="C139">
+        <v>37</v>
+      </c>
+      <c r="D139">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="140" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A140" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="B140" t="s">
+        <v>73</v>
+      </c>
+      <c r="C140">
+        <v>37</v>
+      </c>
+      <c r="D140">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="141" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A141" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="B141" t="s">
+        <v>74</v>
+      </c>
+      <c r="C141">
+        <v>37</v>
+      </c>
+      <c r="D141">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="142" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A142" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="B142" t="s">
+        <v>75</v>
+      </c>
+      <c r="C142">
+        <v>37</v>
+      </c>
+      <c r="D142">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="143" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A143" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="B143" t="s">
+        <v>76</v>
+      </c>
+      <c r="C143">
+        <v>37</v>
+      </c>
+      <c r="D143">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="144" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A144" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="B144" t="s">
+        <v>77</v>
+      </c>
+      <c r="C144">
+        <v>37</v>
+      </c>
+      <c r="D144">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="145" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A145" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="B145" t="s">
+        <v>78</v>
+      </c>
+      <c r="C145">
+        <v>37</v>
+      </c>
+      <c r="D145">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="146" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A146" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="B146" t="s">
+        <v>79</v>
+      </c>
+      <c r="C146">
+        <v>43</v>
+      </c>
+      <c r="D146">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="147" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A147" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="B147" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C147">
+        <v>16</v>
+      </c>
+      <c r="D147">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="148" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A148" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="B148" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C148">
+        <v>16</v>
+      </c>
+      <c r="D148">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="149" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A149" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="B149" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C149">
+        <v>16</v>
+      </c>
+      <c r="D149">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="150" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A150" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="B150" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C150">
+        <v>16</v>
+      </c>
+      <c r="D150">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="151" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A151" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="B151" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C151">
+        <v>16</v>
+      </c>
+      <c r="D151">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="152" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A152" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="B152" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C152">
+        <v>16</v>
+      </c>
+      <c r="D152">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="153" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A153" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="B153" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C153">
+        <v>16</v>
+      </c>
+      <c r="D153">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="154" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A154" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="B154" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C154">
+        <v>20</v>
+      </c>
+      <c r="D154">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="155" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A155" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="B155" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C155">
+        <v>20</v>
+      </c>
+      <c r="D155">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="156" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A156" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="B156" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C156">
+        <v>20</v>
+      </c>
+      <c r="D156">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="157" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A157" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="B157" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C157">
+        <v>20</v>
+      </c>
+      <c r="D157">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="158" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A158" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="B158" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C158">
+        <v>20</v>
+      </c>
+      <c r="D158">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="159" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A159" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="B159" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C159">
+        <v>20</v>
+      </c>
+      <c r="D159">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="160" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A160" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="B160" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C160">
+        <v>25</v>
+      </c>
+      <c r="D160">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="161" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A161" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="B161" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C161">
+        <v>25</v>
+      </c>
+      <c r="D161">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="162" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A162" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="B162" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C162">
+        <v>25</v>
+      </c>
+      <c r="D162">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="163" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A163" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="B163" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C163">
+        <v>25</v>
+      </c>
+      <c r="D163">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="164" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A164" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="B164" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C164">
+        <v>25</v>
+      </c>
+      <c r="D164">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="165" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A165" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="B165" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C165">
+        <v>25</v>
+      </c>
+      <c r="D165">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="166" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A166" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="B166" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C166">
+        <v>25</v>
+      </c>
+      <c r="D166">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="167" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A167" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="B167" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C167">
+        <v>25</v>
+      </c>
+      <c r="D167">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="168" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A168" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="B168" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C168">
+        <v>25</v>
+      </c>
+      <c r="D168">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="169" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A169" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="B169" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C169">
+        <v>25</v>
+      </c>
+      <c r="D169">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="170" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A170" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="B170" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C170">
+        <v>25</v>
+      </c>
+      <c r="D170">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="171" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A171" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="B171" t="s">
+        <v>35</v>
+      </c>
+      <c r="C171">
+        <v>25</v>
+      </c>
+      <c r="D171">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="172" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A172" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="B172" t="s">
+        <v>36</v>
+      </c>
+      <c r="C172">
+        <v>25</v>
+      </c>
+      <c r="D172">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="173" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A173" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="B173" t="s">
+        <v>37</v>
+      </c>
+      <c r="C173">
+        <v>25</v>
+      </c>
+      <c r="D173">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="174" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A174" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="B174" t="s">
+        <v>38</v>
+      </c>
+      <c r="C174">
+        <v>30</v>
+      </c>
+      <c r="D174">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="175" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A175" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="B175" t="s">
+        <v>10</v>
+      </c>
+      <c r="C175">
+        <v>30</v>
+      </c>
+      <c r="D175">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="176" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A176" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="B176" t="s">
+        <v>39</v>
+      </c>
+      <c r="C176">
+        <v>30</v>
+      </c>
+      <c r="D176">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="177" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A177" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="B177" t="s">
+        <v>40</v>
+      </c>
+      <c r="C177">
+        <v>30</v>
+      </c>
+      <c r="D177">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="178" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A178" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="B178" t="s">
+        <v>41</v>
+      </c>
+      <c r="C178">
+        <v>30</v>
+      </c>
+      <c r="D178">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="179" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A179" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="B179" t="s">
+        <v>42</v>
+      </c>
+      <c r="C179">
+        <v>30</v>
+      </c>
+      <c r="D179">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="180" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A180" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="B180" t="s">
+        <v>43</v>
+      </c>
+      <c r="C180">
+        <v>30</v>
+      </c>
+      <c r="D180">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="181" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A181" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="B181" t="s">
+        <v>44</v>
+      </c>
+      <c r="C181">
+        <v>30</v>
+      </c>
+      <c r="D181">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="182" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A182" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="B182" t="s">
+        <v>45</v>
+      </c>
+      <c r="C182">
+        <v>30</v>
+      </c>
+      <c r="D182">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="183" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A183" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="B183" t="s">
+        <v>46</v>
+      </c>
+      <c r="C183">
+        <v>30</v>
+      </c>
+      <c r="D183">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="184" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A184" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="B184" t="s">
+        <v>47</v>
+      </c>
+      <c r="C184">
+        <v>30</v>
+      </c>
+      <c r="D184">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="185" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A185" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="B185" t="s">
+        <v>48</v>
+      </c>
+      <c r="C185">
+        <v>30</v>
+      </c>
+      <c r="D185">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="186" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A186" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="B186" t="s">
+        <v>49</v>
+      </c>
+      <c r="C186">
+        <v>30</v>
+      </c>
+      <c r="D186">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="187" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A187" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="B187" t="s">
+        <v>50</v>
+      </c>
+      <c r="C187">
+        <v>30</v>
+      </c>
+      <c r="D187">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="188" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A188" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="B188" t="s">
+        <v>51</v>
+      </c>
+      <c r="C188">
+        <v>36</v>
+      </c>
+      <c r="D188">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="189" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A189" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="B189" t="s">
+        <v>11</v>
+      </c>
+      <c r="C189">
+        <v>36</v>
+      </c>
+      <c r="D189">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="190" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A190" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="B190" t="s">
+        <v>52</v>
+      </c>
+      <c r="C190">
+        <v>36</v>
+      </c>
+      <c r="D190">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="191" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A191" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="B191" t="s">
+        <v>53</v>
+      </c>
+      <c r="C191">
+        <v>36</v>
+      </c>
+      <c r="D191">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="192" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A192" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="B192" t="s">
+        <v>54</v>
+      </c>
+      <c r="C192">
+        <v>36</v>
+      </c>
+      <c r="D192">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="193" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A193" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="B193" t="s">
+        <v>55</v>
+      </c>
+      <c r="C193">
+        <v>36</v>
+      </c>
+      <c r="D193">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="194" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A194" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="B194" t="s">
+        <v>56</v>
+      </c>
+      <c r="C194">
+        <v>36</v>
+      </c>
+      <c r="D194">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="195" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A195" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="B195" t="s">
+        <v>57</v>
+      </c>
+      <c r="C195">
+        <v>36</v>
+      </c>
+      <c r="D195">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="196" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A196" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="B196" t="s">
+        <v>58</v>
+      </c>
+      <c r="C196">
+        <v>36</v>
+      </c>
+      <c r="D196">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="197" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A197" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="B197" t="s">
+        <v>59</v>
+      </c>
+      <c r="C197">
+        <v>36</v>
+      </c>
+      <c r="D197">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="198" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A198" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="B198" t="s">
+        <v>60</v>
+      </c>
+      <c r="C198">
+        <v>36</v>
+      </c>
+      <c r="D198">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="199" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A199" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="B199" t="s">
+        <v>61</v>
+      </c>
+      <c r="C199">
+        <v>36</v>
+      </c>
+      <c r="D199">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="200" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A200" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="B200" t="s">
+        <v>62</v>
+      </c>
+      <c r="C200">
+        <v>36</v>
+      </c>
+      <c r="D200">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="201" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A201" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="B201" t="s">
+        <v>63</v>
+      </c>
+      <c r="C201">
+        <v>36</v>
+      </c>
+      <c r="D201">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="202" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A202" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="B202" t="s">
+        <v>64</v>
+      </c>
+      <c r="C202">
+        <v>36</v>
+      </c>
+      <c r="D202">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="203" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A203" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="B203" t="s">
+        <v>65</v>
+      </c>
+      <c r="C203">
+        <v>42</v>
+      </c>
+      <c r="D203">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="204" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A204" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="B204" t="s">
+        <v>12</v>
+      </c>
+      <c r="C204">
+        <v>42</v>
+      </c>
+      <c r="D204">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="205" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A205" s="1" t="s">
+        <v>282</v>
+      </c>
+      <c r="B205" t="s">
+        <v>66</v>
+      </c>
+      <c r="C205">
+        <v>42</v>
+      </c>
+      <c r="D205">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="206" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A206" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="B206" t="s">
+        <v>67</v>
+      </c>
+      <c r="C206">
+        <v>42</v>
+      </c>
+      <c r="D206">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="207" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A207" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="B207" t="s">
+        <v>68</v>
+      </c>
+      <c r="C207">
+        <v>42</v>
+      </c>
+      <c r="D207">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="208" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A208" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="B208" t="s">
+        <v>69</v>
+      </c>
+      <c r="C208">
+        <v>42</v>
+      </c>
+      <c r="D208">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="209" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A209" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="B209" t="s">
+        <v>70</v>
+      </c>
+      <c r="C209">
+        <v>42</v>
+      </c>
+      <c r="D209">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="210" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A210" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="B210" t="s">
+        <v>71</v>
+      </c>
+      <c r="C210">
+        <v>42</v>
+      </c>
+      <c r="D210">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="211" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A211" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="B211" t="s">
+        <v>72</v>
+      </c>
+      <c r="C211">
+        <v>42</v>
+      </c>
+      <c r="D211">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="212" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A212" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="B212" t="s">
+        <v>73</v>
+      </c>
+      <c r="C212">
+        <v>42</v>
+      </c>
+      <c r="D212">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="213" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A213" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="B213" t="s">
+        <v>74</v>
+      </c>
+      <c r="C213">
+        <v>42</v>
+      </c>
+      <c r="D213">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="214" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A214" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="B214" t="s">
+        <v>75</v>
+      </c>
+      <c r="C214">
+        <v>42</v>
+      </c>
+      <c r="D214">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="215" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A215" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="B215" t="s">
+        <v>76</v>
+      </c>
+      <c r="C215">
+        <v>42</v>
+      </c>
+      <c r="D215">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="216" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A216" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="B216" t="s">
+        <v>77</v>
+      </c>
+      <c r="C216">
+        <v>42</v>
+      </c>
+      <c r="D216">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="217" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A217" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="B217" t="s">
+        <v>78</v>
+      </c>
+      <c r="C217">
+        <v>42</v>
+      </c>
+      <c r="D217">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="218" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A218" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="B218" t="s">
+        <v>79</v>
+      </c>
+      <c r="C218">
+        <v>49</v>
+      </c>
+      <c r="D218">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="219" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A219" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="B219" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C219">
+        <v>17</v>
+      </c>
+      <c r="D219">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="220" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A220" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="B220" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C220">
+        <v>17</v>
+      </c>
+      <c r="D220">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="221" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A221" s="1" t="s">
+        <v>298</v>
+      </c>
+      <c r="B221" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C221">
+        <v>17</v>
+      </c>
+      <c r="D221">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="222" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A222" s="1" t="s">
+        <v>299</v>
+      </c>
+      <c r="B222" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C222">
+        <v>17</v>
+      </c>
+      <c r="D222">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="223" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A223" s="1" t="s">
+        <v>300</v>
+      </c>
+      <c r="B223" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C223">
+        <v>17</v>
+      </c>
+      <c r="D223">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="224" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A224" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="B224" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C224">
+        <v>17</v>
+      </c>
+      <c r="D224">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="225" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A225" s="1" t="s">
+        <v>302</v>
+      </c>
+      <c r="B225" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C225">
+        <v>17</v>
+      </c>
+      <c r="D225">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="226" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A226" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="B226" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C226">
+        <v>22</v>
+      </c>
+      <c r="D226">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="227" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A227" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="B227" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C227">
+        <v>22</v>
+      </c>
+      <c r="D227">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="228" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A228" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="B228" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C228">
+        <v>22</v>
+      </c>
+      <c r="D228">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="229" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A229" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="B229" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C229">
+        <v>22</v>
+      </c>
+      <c r="D229">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="230" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A230" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="B230" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C230">
+        <v>22</v>
+      </c>
+      <c r="D230">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="231" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A231" s="1" t="s">
+        <v>308</v>
+      </c>
+      <c r="B231" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C231">
+        <v>22</v>
+      </c>
+      <c r="D231">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="232" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A232" s="1" t="s">
+        <v>309</v>
+      </c>
+      <c r="B232" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C232">
+        <v>28</v>
+      </c>
+      <c r="D232">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="233" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A233" s="1" t="s">
+        <v>310</v>
+      </c>
+      <c r="B233" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C233">
+        <v>28</v>
+      </c>
+      <c r="D233">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="234" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A234" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="B234" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C234">
+        <v>28</v>
+      </c>
+      <c r="D234">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="235" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A235" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="B235" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C235">
+        <v>28</v>
+      </c>
+      <c r="D235">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="236" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A236" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="B236" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C236">
+        <v>28</v>
+      </c>
+      <c r="D236">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="237" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A237" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="B237" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C237">
+        <v>28</v>
+      </c>
+      <c r="D237">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="238" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A238" s="1" t="s">
+        <v>315</v>
+      </c>
+      <c r="B238" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C238">
+        <v>28</v>
+      </c>
+      <c r="D238">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="239" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A239" s="1" t="s">
+        <v>316</v>
+      </c>
+      <c r="B239" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C239">
+        <v>28</v>
+      </c>
+      <c r="D239">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="240" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A240" s="1" t="s">
+        <v>317</v>
+      </c>
+      <c r="B240" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C240">
+        <v>28</v>
+      </c>
+      <c r="D240">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="241" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A241" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="B241" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C241">
+        <v>28</v>
+      </c>
+      <c r="D241">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="242" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A242" s="1" t="s">
+        <v>319</v>
+      </c>
+      <c r="B242" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C242">
+        <v>28</v>
+      </c>
+      <c r="D242">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="243" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A243" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="B243" t="s">
+        <v>35</v>
+      </c>
+      <c r="C243">
+        <v>28</v>
+      </c>
+      <c r="D243">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="244" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A244" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="B244" t="s">
+        <v>36</v>
+      </c>
+      <c r="C244">
+        <v>28</v>
+      </c>
+      <c r="D244">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="245" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A245" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="B245" t="s">
+        <v>37</v>
+      </c>
+      <c r="C245">
+        <v>28</v>
+      </c>
+      <c r="D245">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="246" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A246" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="B246" t="s">
+        <v>38</v>
+      </c>
+      <c r="C246">
+        <v>33</v>
+      </c>
+      <c r="D246">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="247" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A247" s="1" t="s">
+        <v>324</v>
+      </c>
+      <c r="B247" t="s">
+        <v>10</v>
+      </c>
+      <c r="C247">
+        <v>33</v>
+      </c>
+      <c r="D247">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="248" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A248" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="B248" t="s">
+        <v>39</v>
+      </c>
+      <c r="C248">
+        <v>33</v>
+      </c>
+      <c r="D248">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="249" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A249" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="B249" t="s">
+        <v>40</v>
+      </c>
+      <c r="C249">
+        <v>33</v>
+      </c>
+      <c r="D249">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="250" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A250" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="B250" t="s">
+        <v>41</v>
+      </c>
+      <c r="C250">
+        <v>33</v>
+      </c>
+      <c r="D250">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="251" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A251" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="B251" t="s">
+        <v>42</v>
+      </c>
+      <c r="C251">
+        <v>33</v>
+      </c>
+      <c r="D251">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="252" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A252" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="B252" t="s">
+        <v>43</v>
+      </c>
+      <c r="C252">
+        <v>33</v>
+      </c>
+      <c r="D252">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="253" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A253" s="1" t="s">
+        <v>330</v>
+      </c>
+      <c r="B253" t="s">
+        <v>44</v>
+      </c>
+      <c r="C253">
+        <v>33</v>
+      </c>
+      <c r="D253">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="254" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A254" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="B254" t="s">
+        <v>45</v>
+      </c>
+      <c r="C254">
+        <v>33</v>
+      </c>
+      <c r="D254">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="255" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A255" s="1" t="s">
+        <v>332</v>
+      </c>
+      <c r="B255" t="s">
+        <v>46</v>
+      </c>
+      <c r="C255">
+        <v>33</v>
+      </c>
+      <c r="D255">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="256" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A256" s="1" t="s">
+        <v>333</v>
+      </c>
+      <c r="B256" t="s">
+        <v>47</v>
+      </c>
+      <c r="C256">
+        <v>33</v>
+      </c>
+      <c r="D256">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="257" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A257" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="B257" t="s">
+        <v>48</v>
+      </c>
+      <c r="C257">
+        <v>33</v>
+      </c>
+      <c r="D257">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="258" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A258" s="1" t="s">
+        <v>335</v>
+      </c>
+      <c r="B258" t="s">
+        <v>49</v>
+      </c>
+      <c r="C258">
+        <v>33</v>
+      </c>
+      <c r="D258">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="259" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A259" s="1" t="s">
+        <v>336</v>
+      </c>
+      <c r="B259" t="s">
+        <v>50</v>
+      </c>
+      <c r="C259">
+        <v>33</v>
+      </c>
+      <c r="D259">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="260" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A260" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="B260" t="s">
+        <v>51</v>
+      </c>
+      <c r="C260">
+        <v>40</v>
+      </c>
+      <c r="D260">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="261" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A261" s="1" t="s">
+        <v>338</v>
+      </c>
+      <c r="B261" t="s">
+        <v>11</v>
+      </c>
+      <c r="C261">
+        <v>40</v>
+      </c>
+      <c r="D261">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="262" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A262" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="B262" t="s">
+        <v>52</v>
+      </c>
+      <c r="C262">
+        <v>40</v>
+      </c>
+      <c r="D262">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="263" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A263" s="1" t="s">
+        <v>340</v>
+      </c>
+      <c r="B263" t="s">
+        <v>53</v>
+      </c>
+      <c r="C263">
+        <v>40</v>
+      </c>
+      <c r="D263">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="264" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A264" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="B264" t="s">
+        <v>54</v>
+      </c>
+      <c r="C264">
+        <v>40</v>
+      </c>
+      <c r="D264">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="265" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A265" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="B265" t="s">
+        <v>55</v>
+      </c>
+      <c r="C265">
+        <v>40</v>
+      </c>
+      <c r="D265">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="266" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A266" s="1" t="s">
+        <v>343</v>
+      </c>
+      <c r="B266" t="s">
+        <v>56</v>
+      </c>
+      <c r="C266">
+        <v>40</v>
+      </c>
+      <c r="D266">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="267" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A267" s="1" t="s">
+        <v>344</v>
+      </c>
+      <c r="B267" t="s">
+        <v>57</v>
+      </c>
+      <c r="C267">
+        <v>40</v>
+      </c>
+      <c r="D267">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="268" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A268" s="1" t="s">
+        <v>345</v>
+      </c>
+      <c r="B268" t="s">
+        <v>58</v>
+      </c>
+      <c r="C268">
+        <v>40</v>
+      </c>
+      <c r="D268">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="269" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A269" s="1" t="s">
+        <v>346</v>
+      </c>
+      <c r="B269" t="s">
+        <v>59</v>
+      </c>
+      <c r="C269">
+        <v>40</v>
+      </c>
+      <c r="D269">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="270" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A270" s="1" t="s">
+        <v>347</v>
+      </c>
+      <c r="B270" t="s">
+        <v>60</v>
+      </c>
+      <c r="C270">
+        <v>40</v>
+      </c>
+      <c r="D270">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="271" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A271" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="B271" t="s">
+        <v>61</v>
+      </c>
+      <c r="C271">
+        <v>40</v>
+      </c>
+      <c r="D271">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="272" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A272" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="B272" t="s">
+        <v>62</v>
+      </c>
+      <c r="C272">
+        <v>40</v>
+      </c>
+      <c r="D272">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="273" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A273" s="1" t="s">
+        <v>350</v>
+      </c>
+      <c r="B273" t="s">
+        <v>63</v>
+      </c>
+      <c r="C273">
+        <v>40</v>
+      </c>
+      <c r="D273">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="274" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A274" s="1" t="s">
+        <v>351</v>
+      </c>
+      <c r="B274" t="s">
+        <v>64</v>
+      </c>
+      <c r="C274">
+        <v>40</v>
+      </c>
+      <c r="D274">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="275" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A275" s="1" t="s">
+        <v>352</v>
+      </c>
+      <c r="B275" t="s">
+        <v>65</v>
+      </c>
+      <c r="C275">
+        <v>47</v>
+      </c>
+      <c r="D275">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="276" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A276" s="1" t="s">
+        <v>353</v>
+      </c>
+      <c r="B276" t="s">
+        <v>12</v>
+      </c>
+      <c r="C276">
+        <v>47</v>
+      </c>
+      <c r="D276">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="277" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A277" s="1" t="s">
+        <v>354</v>
+      </c>
+      <c r="B277" t="s">
+        <v>66</v>
+      </c>
+      <c r="C277">
+        <v>47</v>
+      </c>
+      <c r="D277">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="278" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A278" s="1" t="s">
+        <v>355</v>
+      </c>
+      <c r="B278" t="s">
+        <v>67</v>
+      </c>
+      <c r="C278">
+        <v>47</v>
+      </c>
+      <c r="D278">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="279" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A279" s="1" t="s">
+        <v>356</v>
+      </c>
+      <c r="B279" t="s">
+        <v>68</v>
+      </c>
+      <c r="C279">
+        <v>47</v>
+      </c>
+      <c r="D279">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="280" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A280" s="1" t="s">
+        <v>357</v>
+      </c>
+      <c r="B280" t="s">
+        <v>69</v>
+      </c>
+      <c r="C280">
+        <v>47</v>
+      </c>
+      <c r="D280">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="281" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A281" s="1" t="s">
+        <v>358</v>
+      </c>
+      <c r="B281" t="s">
+        <v>70</v>
+      </c>
+      <c r="C281">
+        <v>47</v>
+      </c>
+      <c r="D281">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="282" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A282" s="1" t="s">
+        <v>359</v>
+      </c>
+      <c r="B282" t="s">
+        <v>71</v>
+      </c>
+      <c r="C282">
+        <v>47</v>
+      </c>
+      <c r="D282">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="283" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A283" s="1" t="s">
+        <v>360</v>
+      </c>
+      <c r="B283" t="s">
+        <v>72</v>
+      </c>
+      <c r="C283">
+        <v>47</v>
+      </c>
+      <c r="D283">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="284" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A284" s="1" t="s">
+        <v>361</v>
+      </c>
+      <c r="B284" t="s">
+        <v>73</v>
+      </c>
+      <c r="C284">
+        <v>47</v>
+      </c>
+      <c r="D284">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="285" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A285" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="B285" t="s">
+        <v>74</v>
+      </c>
+      <c r="C285">
+        <v>47</v>
+      </c>
+      <c r="D285">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="286" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A286" s="1" t="s">
+        <v>363</v>
+      </c>
+      <c r="B286" t="s">
+        <v>75</v>
+      </c>
+      <c r="C286">
+        <v>47</v>
+      </c>
+      <c r="D286">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="287" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A287" s="1" t="s">
+        <v>364</v>
+      </c>
+      <c r="B287" t="s">
+        <v>76</v>
+      </c>
+      <c r="C287">
+        <v>47</v>
+      </c>
+      <c r="D287">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="288" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A288" s="1" t="s">
+        <v>365</v>
+      </c>
+      <c r="B288" t="s">
+        <v>77</v>
+      </c>
+      <c r="C288">
+        <v>47</v>
+      </c>
+      <c r="D288">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="289" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A289" s="1" t="s">
+        <v>366</v>
+      </c>
+      <c r="B289" t="s">
+        <v>78</v>
+      </c>
+      <c r="C289">
+        <v>47</v>
+      </c>
+      <c r="D289">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="290" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A290" s="1" t="s">
+        <v>367</v>
+      </c>
+      <c r="B290" t="s">
+        <v>79</v>
+      </c>
+      <c r="C290">
+        <v>54</v>
+      </c>
+      <c r="D290">
+        <v>58</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>